--- a/Tools/excel2json/excel/UnitDefine.xlsx
+++ b/Tools/excel2json/excel/UnitDefine.xlsx
@@ -1514,16 +1514,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M4" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O4" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="P4" s="3">
         <v>100</v>
@@ -1597,16 +1597,16 @@
         <v>30</v>
       </c>
       <c r="L5" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M5" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N5" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="O5" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="P5" s="3">
         <v>100</v>
@@ -1686,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O6" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="P6" s="3">
         <v>100</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O7" s="3">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="P7" s="3">
         <v>100</v>
@@ -1831,31 +1831,31 @@
         <v>3000</v>
       </c>
       <c r="G8" s="3">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
       </c>
       <c r="J8" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M8" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N8" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>

--- a/Tools/excel2json/excel/UnitDefine.xlsx
+++ b/Tools/excel2json/excel/UnitDefine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18360"/>
+    <workbookView windowWidth="24045" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="UnitDefine" sheetId="1" r:id="rId1"/>
@@ -203,7 +203,7 @@
     <t>战士</t>
   </si>
   <si>
-    <t>Prefabs/Role/DogPBR</t>
+    <t>Prefabs/Role/Tid-0</t>
   </si>
   <si>
     <t>Character</t>
@@ -221,7 +221,7 @@
     <t>法师</t>
   </si>
   <si>
-    <t>Prefabs/Role/PolyArtWizardStandardMat</t>
+    <t>Prefabs/Role/Tid-1</t>
   </si>
   <si>
     <t>血低高魔伤</t>
